--- a/exports/HINDPETRO_full_report.xlsx
+++ b/exports/HINDPETRO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>7.09</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>174.65</v>
+        <v>172.55</v>
       </c>
       <c r="I2" t="n">
         <v>174.5284886862343</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.37</v>
+        <v>-4.54</v>
       </c>
       <c r="L2" t="n">
-        <v>3.71</v>
+        <v>5.06</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.18</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44601.55208333334</v>
+        <v>44602.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>163.15</v>
+        <v>165.6</v>
       </c>
       <c r="I3" t="n">
         <v>165.5735906106326</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>5.45</v>
+        <v>4.03</v>
       </c>
       <c r="L3" t="n">
         <v>4.23</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.22</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>160</v>
+        <v>151.7</v>
       </c>
       <c r="I4" t="n">
         <v>156.7517832131586</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.38</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>12.05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="N4" t="n">
-        <v>4.45</v>
+        <v>6.87</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.57</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.38541666666</v>
+        <v>44631.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>158.95</v>
+        <v>162.8</v>
       </c>
       <c r="I5" t="n">
         <v>160.266641765325</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.78</v>
+        <v>-7.32</v>
       </c>
       <c r="L5" t="n">
-        <v>5.44</v>
+        <v>7.68</v>
       </c>
       <c r="M5" t="n">
         <v>2.24</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>146.05</v>
+        <v>143.6</v>
       </c>
       <c r="I6" t="n">
         <v>144.1068041260457</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>-10.29</v>
+        <v>-11.79</v>
       </c>
       <c r="L6" t="n">
-        <v>11.09</v>
+        <v>12.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.4</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>8.06</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44656.55208333334</v>
+        <v>44657.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>154.85</v>
+        <v>158.55</v>
       </c>
       <c r="I7" t="n">
         <v>155.1691285464142</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.83</v>
+        <v>-10.41</v>
       </c>
       <c r="L7" t="n">
-        <v>8.460000000000001</v>
+        <v>10.76</v>
       </c>
       <c r="M7" t="n">
         <v>1.43</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
         <v>-1.68</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>7.54</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>160.9</v>
+        <v>155.45</v>
       </c>
       <c r="I8" t="n">
         <v>156.613465421995</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>1.48</v>
+        <v>-1.96</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="N8" t="n">
         <v>4.76</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.76</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44671.55208333334</v>
+        <v>44672.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>165.75</v>
+        <v>167.8</v>
       </c>
       <c r="I9" t="n">
         <v>166.4788208476696</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.63</v>
+        <v>-7.94</v>
       </c>
       <c r="L9" t="n">
-        <v>7.94</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>1.81</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44678.55208333334</v>
+        <v>44679.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>154.8</v>
+        <v>153.05</v>
       </c>
       <c r="I10" t="n">
         <v>154.6798618948936</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.75</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>8.1</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>1.43</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.02</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44743.38541666666</v>
+        <v>44743.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>118.9</v>
+        <v>121.05</v>
       </c>
       <c r="I11" t="n">
         <v>120.2080761562195</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>22.31</v>
+        <v>20.91</v>
       </c>
       <c r="L11" t="n">
         <v>2.81</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>9.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>143.45</v>
+        <v>133.75</v>
       </c>
       <c r="I12" t="n">
         <v>135.767608240036</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>49</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>18.5</v>
+        <v>10.49</v>
       </c>
       <c r="L12" t="n">
         <v>2.19</v>
       </c>
       <c r="M12" t="n">
-        <v>3.79</v>
+        <v>6.41</v>
       </c>
       <c r="N12" t="n">
-        <v>5.78</v>
+        <v>7.39</v>
       </c>
       <c r="O12" t="n">
         <v>5.91</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44812.38541666666</v>
+        <v>44812.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>135.2</v>
+        <v>135.8</v>
       </c>
       <c r="I13" t="n">
         <v>135.3106242380569</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.08</v>
+        <v>-1.53</v>
       </c>
       <c r="L13" t="n">
         <v>3.25</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.39</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>127.6</v>
+        <v>123.25</v>
       </c>
       <c r="I14" t="n">
         <v>127.1222367443028</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.04</v>
+        <v>-9.24</v>
       </c>
       <c r="L14" t="n">
-        <v>6.26</v>
+        <v>9.35</v>
       </c>
       <c r="M14" t="n">
         <v>0.79</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>4.15</v>
       </c>
       <c r="O14" t="n">
         <v>3.51</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44862.38541666666</v>
+        <v>44862.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>110.8</v>
+        <v>111.55</v>
       </c>
       <c r="I15" t="n">
         <v>111.3358343480401</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>10.1</v>
+        <v>9.49</v>
       </c>
       <c r="L15" t="n">
         <v>4.22</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.34</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44868.55208333334</v>
+        <v>44869.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>110.75</v>
+        <v>105.35</v>
       </c>
       <c r="I16" t="n">
         <v>107.651942897782</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.72</v>
+        <v>-5.56</v>
       </c>
       <c r="L16" t="n">
-        <v>1.03</v>
+        <v>6.14</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04</v>
+        <v>2.44</v>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>3.93</v>
       </c>
       <c r="O16" t="n">
         <v>0.59</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>109.7</v>
+        <v>113.2</v>
       </c>
       <c r="I17" t="n">
         <v>113.1288752647653</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.13</v>
+        <v>-7.45</v>
       </c>
       <c r="L17" t="n">
-        <v>5.84</v>
+        <v>8.16</v>
       </c>
       <c r="M17" t="n">
         <v>1.23</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.17</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44900.55208333334</v>
+        <v>44901.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>122.55</v>
+        <v>119.55</v>
       </c>
       <c r="I18" t="n">
         <v>120.9972848808347</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>8.26</v>
+        <v>5.61</v>
       </c>
       <c r="L18" t="n">
         <v>2.83</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>7.75</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>125.7</v>
+        <v>129.85</v>
       </c>
       <c r="I19" t="n">
         <v>126.1087592677719</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.14</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>6.4</v>
+        <v>10.25</v>
       </c>
       <c r="M19" t="n">
-        <v>1.64</v>
+        <v>2.47</v>
       </c>
       <c r="N19" t="n">
         <v>4.58</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.08</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>126.65</v>
+        <v>123.65</v>
       </c>
       <c r="I20" t="n">
         <v>125.1651004406906</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.46</v>
+        <v>-4.77</v>
       </c>
       <c r="L20" t="n">
-        <v>2.54</v>
+        <v>5.04</v>
       </c>
       <c r="M20" t="n">
         <v>0.15</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44930.55208333334</v>
+        <v>44931.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>129.15</v>
+        <v>131.4</v>
       </c>
       <c r="I21" t="n">
         <v>129.9386039597519</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.45</v>
+        <v>-6.27</v>
       </c>
       <c r="L21" t="n">
-        <v>6.19</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="N21" t="n">
-        <v>1.45</v>
+        <v>2.48</v>
       </c>
       <c r="O21" t="n">
         <v>-4.33</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.47</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44942.55208333334</v>
+        <v>44943.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>133.35</v>
+        <v>130.2</v>
       </c>
       <c r="I22" t="n">
         <v>130.3403465855624</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>1.48</v>
+        <v>-0.91</v>
       </c>
       <c r="L22" t="n">
         <v>1.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.93</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44994.38541666666</v>
+        <v>44994.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>120.05</v>
+        <v>120.5</v>
       </c>
       <c r="I23" t="n">
         <v>120.0701094533147</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>7.8</v>
+        <v>7.45</v>
       </c>
       <c r="L23" t="n">
         <v>4.95</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.57</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45013.55208333334</v>
+        <v>45014.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>124.95</v>
+        <v>123.85</v>
       </c>
       <c r="I24" t="n">
         <v>124.213404597587</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>3.69</v>
+        <v>2.78</v>
       </c>
       <c r="L24" t="n">
         <v>1.37</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.09</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45035.38541666666</v>
+        <v>45035.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>125.15</v>
+        <v>128</v>
       </c>
       <c r="I25" t="n">
         <v>125.562246439714</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.05</v>
+        <v>-3.35</v>
       </c>
       <c r="L25" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="M25" t="n">
         <v>0.67</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.72</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>160.65</v>
+        <v>153.95</v>
       </c>
       <c r="I26" t="n">
         <v>158.4118894522363</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>99</v>
+        <v>99.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>25.51</v>
+        <v>20.27</v>
       </c>
       <c r="L26" t="n">
         <v>2.73</v>
@@ -1923,7 +2234,7 @@
         <v>1.49</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>4.54</v>
       </c>
       <c r="O26" t="n">
         <v>5.31</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.57</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45177.38541666666</v>
+        <v>45177.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>138.45</v>
+        <v>141.35</v>
       </c>
       <c r="I27" t="n">
         <v>141.1980304018241</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>10.07</v>
+        <v>8.18</v>
       </c>
       <c r="L27" t="n">
         <v>4.71</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6.04</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>135.85</v>
+        <v>135.35</v>
       </c>
       <c r="I28" t="n">
         <v>135.4431101824778</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.89</v>
+        <v>-4.24</v>
       </c>
       <c r="L28" t="n">
-        <v>4.7</v>
+        <v>4.92</v>
       </c>
       <c r="M28" t="n">
         <v>1.68</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>6.23</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>139.25</v>
+        <v>142.6</v>
       </c>
       <c r="I29" t="n">
         <v>142.5642366446389</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.88</v>
+        <v>-5.36</v>
       </c>
       <c r="L29" t="n">
-        <v>5.13</v>
+        <v>7.24</v>
       </c>
       <c r="M29" t="n">
         <v>2.74</v>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
         <v>-2.49</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>6.5</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>136.6</v>
+        <v>134.15</v>
       </c>
       <c r="I30" t="n">
         <v>134.305266589712</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.21</v>
+        <v>-5.93</v>
       </c>
       <c r="L30" t="n">
-        <v>5.05</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
         <v>0.74</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>138.45</v>
+        <v>140.1</v>
       </c>
       <c r="I31" t="n">
         <v>138.9592673964634</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.21</v>
+        <v>-4.44</v>
       </c>
       <c r="L31" t="n">
-        <v>4.55</v>
+        <v>5.18</v>
       </c>
       <c r="M31" t="n">
         <v>1.38</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45250.55208333334</v>
+        <v>45251.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>170.85</v>
+        <v>166.15</v>
       </c>
       <c r="I32" t="n">
         <v>166.1914906727297</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K32" t="n">
-        <v>21.95</v>
+        <v>18.59</v>
       </c>
       <c r="L32" t="n">
         <v>1.43</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>10.48</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45253.38541666666</v>
+        <v>45253.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>174.4</v>
+        <v>182</v>
       </c>
       <c r="I33" t="n">
         <v>181.7855226553939</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.97</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>5.27</v>
+        <v>10.89</v>
       </c>
       <c r="M33" t="n">
         <v>0.71</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.35</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45316.38541666666</v>
+        <v>45316.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>257.95</v>
+        <v>247.4</v>
       </c>
       <c r="I34" t="n">
         <v>252.8805568473479</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>62.83333333333334</v>
+        <v>63</v>
       </c>
       <c r="K34" t="n">
-        <v>41.73</v>
+        <v>35.93</v>
       </c>
       <c r="L34" t="n">
         <v>4.4</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>10.93</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>261.25</v>
+        <v>278</v>
       </c>
       <c r="I35" t="n">
         <v>274.4460529634886</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.6</v>
+        <v>-12.37</v>
       </c>
       <c r="L35" t="n">
-        <v>6.67</v>
+        <v>13.32</v>
       </c>
       <c r="M35" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="N35" t="n">
         <v>5.6</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.06</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>316.6</v>
+        <v>302.6</v>
       </c>
       <c r="I36" t="n">
         <v>307.6737554854541</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K36" t="n">
-        <v>13.88</v>
+        <v>8.85</v>
       </c>
       <c r="L36" t="n">
         <v>5.94</v>
@@ -2493,7 +2924,7 @@
         <v>1.45</v>
       </c>
       <c r="N36" t="n">
-        <v>3.48</v>
+        <v>4.42</v>
       </c>
       <c r="O36" t="n">
         <v>4.17</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.46</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45392.38541666666</v>
+        <v>45392.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>286.95</v>
+        <v>291.2</v>
       </c>
       <c r="I37" t="n">
         <v>289.869629291996</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>5.17</v>
+        <v>3.77</v>
       </c>
       <c r="L37" t="n">
         <v>5.14</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.29</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45422.55208333334</v>
+        <v>45425.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>300.25</v>
+        <v>293.35</v>
       </c>
       <c r="I38" t="n">
         <v>297.1520793700358</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>3.11</v>
+        <v>0.74</v>
       </c>
       <c r="L38" t="n">
         <v>6.39</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45435.55208333334</v>
+        <v>45436.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>321.6</v>
+        <v>327.45</v>
       </c>
       <c r="I39" t="n">
         <v>322.2201361779503</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.630000000000001</v>
+        <v>-11.62</v>
       </c>
       <c r="L39" t="n">
-        <v>11.25</v>
+        <v>12.34</v>
       </c>
       <c r="M39" t="n">
         <v>0.98</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.1</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>351</v>
+        <v>301.05</v>
       </c>
       <c r="I40" t="n">
         <v>319.543785501226</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
-        <v>7.19</v>
+        <v>-8.06</v>
       </c>
       <c r="L40" t="n">
-        <v>3.48</v>
+        <v>14.8</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>15.95</v>
       </c>
       <c r="O40" t="n">
         <v>0.98</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>20.44</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45483.55208333334</v>
+        <v>45484.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>301.75</v>
+        <v>316.7</v>
       </c>
       <c r="I41" t="n">
         <v>308.7403849494627</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.23</v>
+        <v>-5.2</v>
       </c>
       <c r="L41" t="n">
         <v>16.56</v>
@@ -2778,7 +3269,7 @@
         <v>3.56</v>
       </c>
       <c r="N41" t="n">
-        <v>2.27</v>
+        <v>3.96</v>
       </c>
       <c r="O41" t="n">
         <v>-15.95</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>401.75</v>
+        <v>390.6</v>
       </c>
       <c r="I42" t="n">
         <v>391.53912638117</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K42" t="n">
-        <v>26.86</v>
+        <v>23.33</v>
       </c>
       <c r="L42" t="n">
         <v>6.8</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45561.38541666666</v>
+        <v>45561.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>386.9</v>
+        <v>391.5</v>
       </c>
       <c r="I43" t="n">
         <v>388.7414206679352</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>0.95</v>
+        <v>-0.23</v>
       </c>
       <c r="L43" t="n">
         <v>3.43</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.31</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>412.2</v>
+        <v>387.25</v>
       </c>
       <c r="I44" t="n">
         <v>389.6938211393094</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>5.29</v>
+        <v>-1.09</v>
       </c>
       <c r="L44" t="n">
         <v>1.55</v>
       </c>
       <c r="M44" t="n">
-        <v>0.18</v>
+        <v>3.55</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="O44" t="n">
         <v>1.44</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45579.55208333334</v>
+        <v>45580.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>375.5</v>
+        <v>392.45</v>
       </c>
       <c r="I45" t="n">
         <v>389.3208900300667</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>3.03</v>
+        <v>-1.34</v>
       </c>
       <c r="L45" t="n">
         <v>3.54</v>
       </c>
       <c r="M45" t="n">
-        <v>1.52</v>
+        <v>2.18</v>
       </c>
       <c r="N45" t="n">
-        <v>2.65</v>
+        <v>4.73</v>
       </c>
       <c r="O45" t="n">
         <v>-6.85</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.52</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>384.1</v>
+        <v>373.45</v>
       </c>
       <c r="I46" t="n">
         <v>375.7058265023372</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.13</v>
+        <v>-4.84</v>
       </c>
       <c r="L46" t="n">
-        <v>2.66</v>
+        <v>5.19</v>
       </c>
       <c r="M46" t="n">
         <v>0.59</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45603.38541666666</v>
+        <v>45603.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>364.5</v>
+        <v>366.05</v>
       </c>
       <c r="I47" t="n">
         <v>365.7748989708552</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="L47" t="n">
         <v>3.37</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45615.38541666666</v>
+        <v>45615.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>342.55</v>
+        <v>334.3</v>
       </c>
       <c r="I48" t="n">
         <v>340.9011099066997</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.42</v>
+        <v>-8.67</v>
       </c>
       <c r="L48" t="n">
-        <v>7.49</v>
+        <v>8.81</v>
       </c>
       <c r="M48" t="n">
         <v>0.53</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45625.38541666666</v>
+        <v>45625.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>351.75</v>
+        <v>356.5</v>
       </c>
       <c r="I49" t="n">
         <v>356.2374469311395</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.22</v>
+        <v>-6.64</v>
       </c>
       <c r="L49" t="n">
         <v>8.029999999999999</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.66</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>381.85</v>
+        <v>363.95</v>
       </c>
       <c r="I50" t="n">
         <v>366.631148571315</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>7.11</v>
+        <v>2.09</v>
       </c>
       <c r="L50" t="n">
         <v>1.43</v>
@@ -3291,7 +3890,7 @@
         <v>1.56</v>
       </c>
       <c r="N50" t="n">
-        <v>2.55</v>
+        <v>5.47</v>
       </c>
       <c r="O50" t="n">
         <v>0.85</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.19</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>292.2</v>
+        <v>303.35</v>
       </c>
       <c r="I51" t="n">
         <v>292.7241989531544</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K51" t="n">
-        <v>19.71</v>
+        <v>16.65</v>
       </c>
       <c r="L51" t="n">
         <v>5.43</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.69</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>384.5</v>
+        <v>366.1</v>
       </c>
       <c r="I52" t="n">
         <v>369.6855094562375</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>99</v>
       </c>
       <c r="K52" t="n">
-        <v>26.75</v>
+        <v>20.69</v>
       </c>
       <c r="L52" t="n">
         <v>4.05</v>
@@ -3405,7 +4028,7 @@
         <v>2.58</v>
       </c>
       <c r="N52" t="n">
-        <v>3.47</v>
+        <v>5.9</v>
       </c>
       <c r="O52" t="n">
         <v>3.71</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.21</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>364.5</v>
+        <v>375.15</v>
       </c>
       <c r="I53" t="n">
         <v>374.2835136064029</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K53" t="n">
-        <v>0.44</v>
+        <v>-2.47</v>
       </c>
       <c r="L53" t="n">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>0.03</v>
+        <v>4.87</v>
       </c>
       <c r="N53" t="n">
-        <v>2.32</v>
+        <v>3.16</v>
       </c>
       <c r="O53" t="n">
         <v>-5.9</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.99</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45852.38541666666</v>
+        <v>45852.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>401.05</v>
+        <v>397.45</v>
       </c>
       <c r="I54" t="n">
         <v>397.510767458633</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>6.9</v>
+        <v>5.94</v>
       </c>
       <c r="L54" t="n">
         <v>0.23</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.48</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>365.2</v>
+        <v>374.7</v>
       </c>
       <c r="I55" t="n">
         <v>373.1363849124385</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>53</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>8.109999999999999</v>
+        <v>5.72</v>
       </c>
       <c r="L55" t="n">
         <v>4.59</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>445.95</v>
+        <v>441.1</v>
       </c>
       <c r="I56" t="n">
         <v>442.8211635949875</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>77</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>19.02</v>
+        <v>17.72</v>
       </c>
       <c r="L56" t="n">
         <v>2.5</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>4.56</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>438.35</v>
+        <v>444.85</v>
       </c>
       <c r="I57" t="n">
         <v>440.057030247977</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>0.62</v>
+        <v>-0.85</v>
       </c>
       <c r="L57" t="n">
         <v>1.18</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.69</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46029.38541666666</v>
+        <v>46029.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>455.5</v>
+        <v>451.75</v>
       </c>
       <c r="I58" t="n">
         <v>454.2332131664439</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>2.39</v>
+        <v>1.55</v>
       </c>
       <c r="L58" t="n">
         <v>2.41</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.65</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>410.8</v>
+        <v>425.3</v>
       </c>
       <c r="I59" t="n">
         <v>420.0344234777536</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>9.06</v>
+        <v>5.86</v>
       </c>
       <c r="L59" t="n">
         <v>0.85</v>
       </c>
       <c r="M59" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="N59" t="n">
-        <v>3.85</v>
+        <v>5.01</v>
       </c>
       <c r="O59" t="n">
         <v>-1.12</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>424.05</v>
+        <v>412.05</v>
       </c>
       <c r="I60" t="n">
         <v>415.2498522532853</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.29</v>
+        <v>-3.12</v>
       </c>
       <c r="L60" t="n">
-        <v>3.07</v>
+        <v>3.64</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>313.5</v>
+        <v>345.85</v>
       </c>
       <c r="I61" t="n">
         <v>337.4214600543157</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K61" t="n">
-        <v>23.92</v>
+        <v>16.07</v>
       </c>
       <c r="L61" t="n">
         <v>4.94</v>
       </c>
       <c r="M61" t="n">
-        <v>4.29</v>
+        <v>7.38</v>
       </c>
       <c r="N61" t="n">
-        <v>4.55</v>
+        <v>10.7</v>
       </c>
       <c r="O61" t="n">
         <v>-5.26</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>12.37</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>354.45</v>
+        <v>352.5</v>
       </c>
       <c r="I62" t="n">
         <v>352.979513155474</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>2.49</v>
+        <v>1.92</v>
       </c>
       <c r="L62" t="n">
         <v>6.29</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.33</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>364.25</v>
+        <v>369.55</v>
       </c>
       <c r="I63" t="n">
         <v>367.6377757263728</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.33</v>
+        <v>-4.84</v>
       </c>
       <c r="L63" t="n">
         <v>5.76</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.44</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>366.35</v>
+        <v>358.05</v>
       </c>
       <c r="I64" t="n">
         <v>361.4128533667778</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.87</v>
+        <v>-3.11</v>
       </c>
       <c r="L64" t="n">
-        <v>2.56</v>
+        <v>4.03</v>
       </c>
       <c r="M64" t="n">
         <v>1.3</v>
       </c>
       <c r="N64" t="n">
-        <v>2.24</v>
+        <v>3.41</v>
       </c>
       <c r="O64" t="n">
         <v>1.44</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>5.72</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>355.35</v>
+        <v>370.6</v>
       </c>
       <c r="I65" t="n">
         <v>368.2464062379725</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>0.75</v>
+        <v>-3.51</v>
       </c>
       <c r="L65" t="n">
-        <v>2.23</v>
+        <v>3.88</v>
       </c>
       <c r="M65" t="n">
         <v>2.86</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>388.95</v>
+        <v>374.25</v>
       </c>
       <c r="I66" t="n">
         <v>374.6043149522941</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>4.95</v>
+        <v>0.98</v>
       </c>
       <c r="L66" t="n">
         <v>4.29</v>
       </c>
       <c r="M66" t="n">
-        <v>0.37</v>
+        <v>0.9</v>
       </c>
       <c r="N66" t="n">
-        <v>2.23</v>
+        <v>4.31</v>
       </c>
       <c r="O66" t="n">
         <v>6.13</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.73</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46223.55208333334</v>
+        <v>46224.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>384.8</v>
+        <v>386.75</v>
       </c>
       <c r="I67" t="n">
         <v>385.6980150072602</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.82</v>
+        <v>-3.34</v>
       </c>
       <c r="L67" t="n">
-        <v>3.59</v>
+        <v>4.17</v>
       </c>
       <c r="M67" t="n">
         <v>0.78</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>4.59</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>375.05</v>
+        <v>362.2</v>
       </c>
       <c r="I68" t="n">
         <v>369.6294894980022</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.03</v>
+        <v>-6.35</v>
       </c>
       <c r="L68" t="n">
-        <v>3.32</v>
+        <v>7.41</v>
       </c>
       <c r="M68" t="n">
-        <v>1.16</v>
+        <v>2.37</v>
       </c>
       <c r="N68" t="n">
         <v>3.04</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.16</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>372.9</v>
+        <v>375</v>
       </c>
       <c r="I69" t="n">
         <v>374.7431564111827</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.95</v>
+        <v>-3.53</v>
       </c>
       <c r="L69" t="n">
         <v>5.45</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>2.76</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>364.8</v>
+        <v>356.8</v>
       </c>
       <c r="I70" t="n">
         <v>364.6459208207608</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.72</v>
+        <v>-4.85</v>
       </c>
       <c r="L70" t="n">
-        <v>2.97</v>
+        <v>5.23</v>
       </c>
       <c r="M70" t="n">
-        <v>0.01</v>
+        <v>0.77</v>
       </c>
       <c r="N70" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="O70" t="n">
         <v>0.51</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>4.94</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>331.95</v>
+        <v>347.85</v>
       </c>
       <c r="I71" t="n">
         <v>343.4899897366734</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K71" t="n">
-        <v>6.96</v>
+        <v>2.51</v>
       </c>
       <c r="L71" t="n">
         <v>2.35</v>
@@ -4488,7 +5339,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N71" t="n">
-        <v>2.27</v>
+        <v>4.87</v>
       </c>
       <c r="O71" t="n">
         <v>-1.82</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>8.25</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>341.5</v>
+        <v>329.7</v>
       </c>
       <c r="I72" t="n">
         <v>331.3546362022215</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.83</v>
+        <v>-5.22</v>
       </c>
       <c r="L72" t="n">
-        <v>4.83</v>
+        <v>5.48</v>
       </c>
       <c r="M72" t="n">
         <v>0.58</v>
       </c>
       <c r="N72" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="O72" t="n">
         <v>4.87</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,12 @@
       <c r="Q73" t="n">
         <v>6</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +7588,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.6</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6717,7 +7598,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -6727,7 +7608,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="8">
@@ -6737,7 +7618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6747,7 +7628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.6</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="10">
@@ -6757,7 +7638,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="11">
@@ -6767,7 +7648,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -6777,7 +7658,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6787,7 +7668,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.2</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="14">
@@ -6797,7 +7678,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.52</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="15">
@@ -6807,7 +7688,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.25</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="16">
@@ -6817,7 +7698,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.74</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="17">
@@ -6827,7 +7708,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.73</v>
+        <v>35.93</v>
       </c>
     </row>
     <row r="18">
@@ -6837,7 +7718,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.1</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="19">
@@ -6847,7 +7728,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="20">
@@ -6857,7 +7738,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -6877,7 +7758,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -6887,7 +7768,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +7778,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="25">
@@ -6907,7 +7788,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.37</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="26">
@@ -6917,7 +7798,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.63</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="27">
@@ -6927,7 +7808,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.22</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="28">
@@ -6937,7 +7818,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
